--- a/test_and_result/test2_enriched_delivery_252.xlsx
+++ b/test_and_result/test2_enriched_delivery_252.xlsx
@@ -1691,7 +1691,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://octopart.com/part/mirka/9A-570-320</t>
+          <t>https://www.nainc.org/product/mirka-abranet-2-3-4-in-x-10-yd-320g-mesh-grip-roll/</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1944,34 +1944,34 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>Product Type</t>
+          <t>Abrasive Material</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>Sanding Disc</t>
+          <t>Aluminum Oxide Mesh</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Brand Name</t>
+          <t>Backing Material</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>Mirka</t>
+          <t>Polyamide Fabric Mesh</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Material Application</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>Mirka USA Inc</t>
+          <t>Dust-Free Woodworking, Automotive, Composites</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr"/>
@@ -1988,534 +1988,490 @@
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Grit</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>2-3/4</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
+          <t>P320</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr"/>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Selling Qty</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr"/>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>Grit</t>
+          <t>Standard Packaging Information</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>P320</t>
+          <t>1 Each</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>Abrasive Material</t>
+          <t>Length</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>Aluminum Oxide Mesh</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr"/>
+          <t>2-3/4</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>Backing Material</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>Polyamide Fabric Mesh</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>Disc Type</t>
+          <t>Product Type</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>Grip Mesh Roll / Strip</t>
+          <t>Sanding Disc</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr"/>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>Material Application</t>
+          <t>Brand Name</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>Dust-Free Woodworking, Automotive, Composites</t>
+          <t>Mirka</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr"/>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>Selling Qty</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Mirka USA Inc</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr"/>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>Selling UOM</t>
+          <t>Warranty</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>Each</t>
+          <t>1 Year Manufacturer, 1 Year Labor and Parts</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr"/>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>Standard Packaging Information</t>
+          <t>Standard/Approvals</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>1 Each</t>
+          <t>ISO 9001 Certified, ANSI Compliant, RoHS Compliant</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr"/>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>Warranty</t>
+          <t>Overall Dimensions</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>1 Year Manufacturer, 1 Year Labor and Parts</t>
+          <t>30 in W x 2-3/4 in L</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr"/>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>Amperage Rating</t>
+          <t>Grit Standard</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+          <t>FEPA P-Grade Standard</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr"/>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>Primary Function</t>
+          <t>Grain Structure</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>Dust-Free Fine Finish Sanding</t>
+          <t>Electrostatic Open Mesh Grain Matrix</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr"/>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>Overall Dimensions</t>
+          <t>Backing Weight</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>30 in W x 2-3/4 in L</t>
+          <t>Net Mesh (Ultra-Flexible)</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr"/>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>Grit Standard</t>
+          <t>Bonding Agent</t>
         </is>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>FEPA P-Grade Standard</t>
+          <t>Resin Over Resin Bond</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr"/>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>Grain Structure</t>
+          <t>Coating Structure</t>
         </is>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>Electrostatic Open Mesh Grain Matrix</t>
+          <t>Net Mesh Permeable Coat</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr"/>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>Backing Weight</t>
+          <t>Cutting Action</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>Net Mesh (Ultra-Flexible)</t>
+          <t>High-Efficiency Dust-Free Smooth Finishing</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr"/>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>Bonding Agent</t>
+          <t>Conformability</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>Resin Over Resin Bond</t>
+          <t>High Contour Conformability</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr"/>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>Coating Structure</t>
+          <t>Anti-Clogging Feature</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>Net Mesh Permeable Coat</t>
+          <t>100% Through-Mesh Dust Evacuation</t>
         </is>
       </c>
       <c r="DT2" t="inlineStr"/>
       <c r="DU2" t="inlineStr">
         <is>
-          <t>Attachment Type</t>
+          <t>Wet or Dry Application</t>
         </is>
       </c>
       <c r="DV2" t="inlineStr">
         <is>
-          <t>Hook and Loop (Grip System)</t>
+          <t>Wet and Dry Compatible</t>
         </is>
       </c>
       <c r="DW2" t="inlineStr"/>
       <c r="DX2" t="inlineStr">
         <is>
-          <t>Hole Pattern</t>
+          <t>Anti-Static Feature</t>
         </is>
       </c>
       <c r="DY2" t="inlineStr">
         <is>
-          <t>Dust-Free Net Mesh Permeable Surface</t>
+          <t>Anti-Static Mesh Matrix for Reduced Dust Attraction</t>
         </is>
       </c>
       <c r="DZ2" t="inlineStr"/>
       <c r="EA2" t="inlineStr">
         <is>
-          <t>Compatible Tools</t>
+          <t>Heat Dissipation</t>
         </is>
       </c>
       <c r="EB2" t="inlineStr">
         <is>
-          <t>Random Orbital Sander, Hand Sanding Block, File Sander</t>
+          <t>Cool Running Formula with Thermal Dissipation</t>
         </is>
       </c>
       <c r="EC2" t="inlineStr"/>
       <c r="ED2" t="inlineStr">
         <is>
-          <t>Mounting Configuration</t>
+          <t>Attachment Type</t>
         </is>
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>Quick-Change Grip Pad Mounting</t>
+          <t>Hook and Loop (Grip System)</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr"/>
       <c r="EG2" t="inlineStr">
         <is>
-          <t>Cutting Action</t>
+          <t>Hole Pattern</t>
         </is>
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>High-Efficiency Dust-Free Smooth Finishing</t>
+          <t>Dust-Free Net Mesh Permeable Surface</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr"/>
       <c r="EJ2" t="inlineStr">
         <is>
-          <t>Conformability</t>
+          <t>Compatible Tools</t>
         </is>
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>High Contour Conformability</t>
+          <t>Random Orbital Sander, Hand Sanding Block, File Sander</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr"/>
       <c r="EM2" t="inlineStr">
         <is>
-          <t>Anti-Clogging Feature</t>
+          <t>Mounting Configuration</t>
         </is>
       </c>
       <c r="EN2" t="inlineStr">
         <is>
-          <t>100% Through-Mesh Dust Evacuation</t>
+          <t>Quick-Change Grip Pad Mounting</t>
         </is>
       </c>
       <c r="EO2" t="inlineStr"/>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>Wet or Dry Application</t>
+          <t>Primary Workpiece Substrate</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr">
         <is>
-          <t>Wet and Dry Compatible</t>
+          <t>Hardwood, Softwood, Primers &amp; Automotive Paint</t>
         </is>
       </c>
       <c r="ER2" t="inlineStr"/>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>Anti-Static Feature</t>
+          <t>Secondary Workpiece Substrate</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>Anti-Static Mesh Matrix for Reduced Dust Attraction</t>
+          <t>Solid Surface Polymers, Gel Coats, Composites</t>
         </is>
       </c>
       <c r="EU2" t="inlineStr"/>
       <c r="EV2" t="inlineStr">
         <is>
-          <t>Heat Dissipation</t>
+          <t>Target Surface Finish</t>
         </is>
       </c>
       <c r="EW2" t="inlineStr">
         <is>
-          <t>Cool Running Formula with Thermal Dissipation</t>
+          <t>Ultra-Fine Scratch-Free Finish</t>
         </is>
       </c>
       <c r="EX2" t="inlineStr"/>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>Primary Workpiece Substrate</t>
+          <t>Primary Function</t>
         </is>
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>Hardwood, Softwood, Primers &amp; Automotive Paint</t>
+          <t>Dust-Free Fine Finish Sanding</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr"/>
       <c r="FB2" t="inlineStr">
         <is>
-          <t>Secondary Workpiece Substrate</t>
+          <t>Package Quantity</t>
         </is>
       </c>
       <c r="FC2" t="inlineStr">
         <is>
-          <t>Solid Surface Polymers, Gel Coats, Composites</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FD2" t="inlineStr"/>
       <c r="FE2" t="inlineStr">
         <is>
-          <t>Target Surface Finish</t>
+          <t>Package Type</t>
         </is>
       </c>
       <c r="FF2" t="inlineStr">
         <is>
-          <t>Ultra-Fine Scratch-Free Finish</t>
+          <t>Grip Roll in Dispenser Carton</t>
         </is>
       </c>
       <c r="FG2" t="inlineStr"/>
       <c r="FH2" t="inlineStr">
         <is>
-          <t>Package Quantity</t>
+          <t>Unit Packaging Weight</t>
         </is>
       </c>
       <c r="FI2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FJ2" t="inlineStr"/>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="FJ2" t="inlineStr">
+        <is>
+          <t>lb</t>
+        </is>
+      </c>
       <c r="FK2" t="inlineStr">
         <is>
-          <t>Package Type</t>
+          <t>Country Of Origin</t>
         </is>
       </c>
       <c r="FL2" t="inlineStr">
         <is>
-          <t>Grip Roll in Dispenser Carton</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="FM2" t="inlineStr"/>
       <c r="FN2" t="inlineStr">
         <is>
-          <t>Unit Packaging Weight</t>
+          <t>Discontinued</t>
         </is>
       </c>
       <c r="FO2" t="inlineStr">
         <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="FP2" t="inlineStr">
-        <is>
-          <t>lb</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="FP2" t="inlineStr"/>
       <c r="FQ2" t="inlineStr">
         <is>
-          <t>Country Of Origin</t>
+          <t>Safety Standard</t>
         </is>
       </c>
       <c r="FR2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>OSHA Safety Standard Compliant</t>
         </is>
       </c>
       <c r="FS2" t="inlineStr"/>
       <c r="FT2" t="inlineStr">
         <is>
-          <t>Discontinued</t>
+          <t>Quality Certification</t>
         </is>
       </c>
       <c r="FU2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>ISO 9001:2015 Quality Management System</t>
         </is>
       </c>
       <c r="FV2" t="inlineStr"/>
       <c r="FW2" t="inlineStr">
         <is>
-          <t>Standard/Approvals</t>
+          <t>Environmental Compliance</t>
         </is>
       </c>
       <c r="FX2" t="inlineStr">
         <is>
-          <t>ISO 9001 Certified, ANSI Compliant, RoHS Compliant</t>
+          <t>RoHS Directive 2011/65/EU Compliant</t>
         </is>
       </c>
       <c r="FY2" t="inlineStr"/>
       <c r="FZ2" t="inlineStr">
         <is>
-          <t>Safety Standard</t>
+          <t>Prop 65</t>
         </is>
       </c>
       <c r="GA2" t="inlineStr">
         <is>
-          <t>OSHA Safety Standard Compliant</t>
+          <t>WARNING: Cancer and Reproductive Harm - www.P65Warnings.ca.gov</t>
         </is>
       </c>
       <c r="GB2" t="inlineStr"/>
       <c r="GC2" t="inlineStr">
         <is>
-          <t>Quality Certification</t>
+          <t>Manufacturer Part Number</t>
         </is>
       </c>
       <c r="GD2" t="inlineStr">
         <is>
-          <t>ISO 9001:2015 Quality Management System</t>
+          <t>9A-570-320</t>
         </is>
       </c>
       <c r="GE2" t="inlineStr"/>
       <c r="GF2" t="inlineStr">
         <is>
-          <t>Environmental Compliance</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="GG2" t="inlineStr">
         <is>
-          <t>RoHS Directive 2011/65/EU Compliant</t>
+          <t>Grey / Mesh Brown</t>
         </is>
       </c>
       <c r="GH2" t="inlineStr"/>
       <c r="GI2" t="inlineStr">
         <is>
-          <t>Prop 65</t>
+          <t>Selling UOM</t>
         </is>
       </c>
       <c r="GJ2" t="inlineStr">
         <is>
-          <t>WARNING: Cancer and Reproductive Harm - www.P65Warnings.ca.gov</t>
+          <t>Each</t>
         </is>
       </c>
       <c r="GK2" t="inlineStr"/>
-      <c r="GL2" t="inlineStr">
-        <is>
-          <t>Manufacturer Part Number</t>
-        </is>
-      </c>
-      <c r="GM2" t="inlineStr">
-        <is>
-          <t>9A-570-320</t>
-        </is>
-      </c>
+      <c r="GL2" t="inlineStr"/>
+      <c r="GM2" t="inlineStr"/>
       <c r="GN2" t="inlineStr"/>
-      <c r="GO2" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="GP2" t="inlineStr">
-        <is>
-          <t>Grey / Mesh Brown</t>
-        </is>
-      </c>
+      <c r="GO2" t="inlineStr"/>
+      <c r="GP2" t="inlineStr"/>
       <c r="GQ2" t="inlineStr"/>
-      <c r="GR2" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
-      </c>
-      <c r="GS2" t="inlineStr">
-        <is>
-          <t>3/4</t>
-        </is>
-      </c>
-      <c r="GT2" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="GU2" t="inlineStr">
-        <is>
-          <t>Arbor Size</t>
-        </is>
-      </c>
-      <c r="GV2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="GW2" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
+      <c r="GR2" t="inlineStr"/>
+      <c r="GS2" t="inlineStr"/>
+      <c r="GT2" t="inlineStr"/>
+      <c r="GU2" t="inlineStr"/>
+      <c r="GV2" t="inlineStr"/>
+      <c r="GW2" t="inlineStr"/>
       <c r="GX2" t="inlineStr">
         <is>
           <t>889948185501</t>
@@ -2743,22 +2699,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.freud.com</t>
+          <t>https://www.qualityworldtools.com/product/freud-dbd090094101f-diablo-9-in-metal-cut-off-disc/</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.freud.com</t>
+          <t>https://www.qualityworldtools.com/product/freud-dbd090094101f-diablo-9-in-metal-cut-off-disc/</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.freud.com/support/DBD090094101F_spec.pdf</t>
+          <t>https://www.toolorbit.com/freud-dbd090094101f-diablo-9-in-metal-cut-off-disc</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.freud.com/documents/DBD090094101F_manual.pdf</t>
+          <t>https://www.qualityworldtools.com/product/freud-dbd090094101f-diablo-9-in-metal-cut-off-disc//documents/DBD090094101F_manual.pdf</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -2860,17 +2816,17 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Freud®, DBD090094101F, Metal Cut-Off Disc</t>
+          <t>Freud®, DBD090094101F, Metal Cut-Off Disc, Aluminum</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Freud® Metal Cut-Off Disc, , Additional Information: Abrasive Material: Premium Aluminum Oxide, Material Application: Metal, Stainless Steel, Trade Name: Diablo®, Max Speed: 13300.</t>
+          <t>Freud® Metal Cut-Off Disc, Aluminum, Additional Information: Abrasive Material: Premium Aluminum Oxide, Material Application: Metal, Stainless Steel, Trade Name: Diablo®, Max Speed: 13300.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Metal Cut-Off Disc</t>
+          <t>Metal Cut-Off Disc, Aluminum</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -2890,92 +2846,92 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
+          <t>Material / Construction: Aluminum</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>Abrasive Material: Premium Aluminum Oxide</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>Material Application: Metal, Stainless Steel</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>Trade Name: Diablo®</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>Max Speed: 13300 rpm</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>Warranty: 1 Year Manufacturer, 1 Year Labor and Parts</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>Premium abrasive grain formulation for fast cutting action</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>Heavy-duty backing for superior tear resistance and extended lifespan</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>Optimized for industrial metalworking, woodworking, and surface prep</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>Brand / Manufacturer: Freud</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>Product Category: Metal Cut-Off Disc</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>Primary Application: Commercial &amp; Residential Metal Cut-Off Disc Applications</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>Standard Packaging: 1 Each</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>Warranty Protection: 1 Year Manufacturer, 1 Year Labor and Parts</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>Engineered for heavy-duty industrial performance and durability</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>Precision manufactured to exact OEM tolerances</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>High tensile strength and wear-resistant construction</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>Resistant to environmental degradation and industrial chemicals</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Optimized for rapid integration and streamlined maintenance</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -3054,501 +3010,501 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>Selling Qty</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Aluminum</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr"/>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>Standard Packaging Information</t>
+          <t>Selling Qty</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1 Each</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr"/>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>Product Type</t>
+          <t>Standard Packaging Information</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>Metal Cut-Off Disc</t>
+          <t>1 Each</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>Brand Name</t>
+          <t>Product Type</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>Freud</t>
+          <t>Metal Cut-Off Disc</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr"/>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Brand Name</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>Freud America Inc</t>
+          <t>Freud</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr"/>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>Warranty</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1 Year Manufacturer, 1 Year Labor and Parts</t>
+          <t>Freud America Inc</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr"/>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>Primary Function</t>
+          <t>Warranty</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>High-Speed Metal Cutting &amp; Severing</t>
+          <t>1 Year Manufacturer, 1 Year Labor and Parts</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr"/>
       <c r="CK3" t="inlineStr">
         <is>
+          <t>Standard/Approvals</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>ISO 9001 Certified, ANSI Compliant, RoHS Compliant</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr"/>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
           <t>Thickness</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>.045</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>in</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
-        <is>
-          <t>Grit Standard</t>
-        </is>
-      </c>
-      <c r="CO3" t="inlineStr">
-        <is>
-          <t>ANSI Standard Grade</t>
-        </is>
-      </c>
-      <c r="CP3" t="inlineStr"/>
-      <c r="CQ3" t="inlineStr">
-        <is>
-          <t>Grain Structure</t>
-        </is>
-      </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>Semi-Friable High-Density Crystalline Grain</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr"/>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>Backing Material</t>
+          <t>Arbor Size</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>Reinforced Fiberglass Mesh Layers</t>
-        </is>
-      </c>
-      <c r="CV3" t="inlineStr"/>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>Backing Weight</t>
+          <t>Overall Dimensions</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>Standard Industrial Weight</t>
+          <t>9 in Dia x .045 in T</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr"/>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>Bonding Agent</t>
+          <t>Grain Structure</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>Phenolic Resin Matrix</t>
+          <t>Semi-Friable High-Density Crystalline Grain</t>
         </is>
       </c>
       <c r="DB3" t="inlineStr"/>
       <c r="DC3" t="inlineStr">
         <is>
-          <t>Coating Structure</t>
+          <t>Backing Material</t>
         </is>
       </c>
       <c r="DD3" t="inlineStr">
         <is>
-          <t>Closed Coat (Maximum Durability)</t>
+          <t>Reinforced Fiberglass Mesh Layers</t>
         </is>
       </c>
       <c r="DE3" t="inlineStr"/>
       <c r="DF3" t="inlineStr">
         <is>
-          <t>Disc Type</t>
+          <t>Backing Weight</t>
         </is>
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>Type 1 Straight Cut-Off Wheel</t>
+          <t>Standard Industrial Weight</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr"/>
       <c r="DI3" t="inlineStr">
         <is>
-          <t>Attachment Type</t>
+          <t>Bonding Agent</t>
         </is>
       </c>
       <c r="DJ3" t="inlineStr">
         <is>
-          <t>7/8 in Center Hole Mount</t>
+          <t>Phenolic Resin Matrix</t>
         </is>
       </c>
       <c r="DK3" t="inlineStr"/>
       <c r="DL3" t="inlineStr">
         <is>
-          <t>Hole Pattern</t>
+          <t>Coating Structure</t>
         </is>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>Solid (No Holes)</t>
+          <t>Closed Coat (Maximum Durability)</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr"/>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>Compatible Tools</t>
+          <t>Max Surface Speed</t>
         </is>
       </c>
       <c r="DP3" t="inlineStr">
         <is>
-          <t>Angle Grinder, Circular Saw, Cut-Off Tool</t>
+          <t>80 m/s (15700 SFPM)</t>
         </is>
       </c>
       <c r="DQ3" t="inlineStr"/>
       <c r="DR3" t="inlineStr">
         <is>
-          <t>Mounting Configuration</t>
+          <t>Cutting Action</t>
         </is>
       </c>
       <c r="DS3" t="inlineStr">
         <is>
-          <t>Flange &amp; Nut Clamping Mount</t>
+          <t>Fast Metal Severing &amp; Rapid Burr-Free Cut</t>
         </is>
       </c>
       <c r="DT3" t="inlineStr"/>
       <c r="DU3" t="inlineStr">
         <is>
-          <t>Max Surface Speed</t>
+          <t>Conformability</t>
         </is>
       </c>
       <c r="DV3" t="inlineStr">
         <is>
-          <t>80 m/s (15700 SFPM)</t>
+          <t>Rigid High-Tensile Wheel</t>
         </is>
       </c>
       <c r="DW3" t="inlineStr"/>
       <c r="DX3" t="inlineStr">
         <is>
-          <t>Cutting Action</t>
+          <t>Anti-Clogging Feature</t>
         </is>
       </c>
       <c r="DY3" t="inlineStr">
         <is>
-          <t>Fast Metal Severing &amp; Rapid Burr-Free Cut</t>
+          <t>Heat-Resistant Open-Pore Structure</t>
         </is>
       </c>
       <c r="DZ3" t="inlineStr"/>
       <c r="EA3" t="inlineStr">
         <is>
-          <t>Conformability</t>
+          <t>Wet or Dry Application</t>
         </is>
       </c>
       <c r="EB3" t="inlineStr">
         <is>
-          <t>Rigid High-Tensile Wheel</t>
+          <t>Dry Sanding &amp; Cutting</t>
         </is>
       </c>
       <c r="EC3" t="inlineStr"/>
       <c r="ED3" t="inlineStr">
         <is>
-          <t>Anti-Clogging Feature</t>
+          <t>Anti-Static Feature</t>
         </is>
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>Heat-Resistant Open-Pore Structure</t>
+          <t>Non-Conductive Matrix</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr"/>
       <c r="EG3" t="inlineStr">
         <is>
-          <t>Wet or Dry Application</t>
+          <t>Heat Dissipation</t>
         </is>
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>Dry Sanding &amp; Cutting</t>
+          <t>Cool Running Formula with Thermal Dissipation</t>
         </is>
       </c>
       <c r="EI3" t="inlineStr"/>
       <c r="EJ3" t="inlineStr">
         <is>
-          <t>Anti-Static Feature</t>
+          <t>Disc Type</t>
         </is>
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>Non-Conductive Matrix</t>
+          <t>Type 1 Straight Cut-Off Wheel</t>
         </is>
       </c>
       <c r="EL3" t="inlineStr"/>
       <c r="EM3" t="inlineStr">
         <is>
-          <t>Heat Dissipation</t>
+          <t>Attachment Type</t>
         </is>
       </c>
       <c r="EN3" t="inlineStr">
         <is>
-          <t>Cool Running Formula with Thermal Dissipation</t>
+          <t>7/8 in Center Hole Mount</t>
         </is>
       </c>
       <c r="EO3" t="inlineStr"/>
       <c r="EP3" t="inlineStr">
         <is>
-          <t>Primary Workpiece Substrate</t>
+          <t>Hole Pattern</t>
         </is>
       </c>
       <c r="EQ3" t="inlineStr">
         <is>
-          <t>Ferrous Metals &amp; Stainless Steel</t>
+          <t>Solid (No Holes)</t>
         </is>
       </c>
       <c r="ER3" t="inlineStr"/>
       <c r="ES3" t="inlineStr">
         <is>
-          <t>Secondary Workpiece Substrate</t>
+          <t>Compatible Tools</t>
         </is>
       </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>Aluminum, Brass, Non-Ferrous Alloys</t>
+          <t>Angle Grinder, Circular Saw, Cut-Off Tool</t>
         </is>
       </c>
       <c r="EU3" t="inlineStr"/>
       <c r="EV3" t="inlineStr">
         <is>
-          <t>Target Surface Finish</t>
+          <t>Mounting Configuration</t>
         </is>
       </c>
       <c r="EW3" t="inlineStr">
         <is>
-          <t>Clean Burr-Free Cut Edge</t>
+          <t>Flange &amp; Nut Clamping Mount</t>
         </is>
       </c>
       <c r="EX3" t="inlineStr"/>
       <c r="EY3" t="inlineStr">
         <is>
-          <t>Package Quantity</t>
+          <t>Primary Workpiece Substrate</t>
         </is>
       </c>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Ferrous Metals &amp; Stainless Steel</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr"/>
       <c r="FB3" t="inlineStr">
         <is>
-          <t>Package Type</t>
+          <t>Secondary Workpiece Substrate</t>
         </is>
       </c>
       <c r="FC3" t="inlineStr">
         <is>
-          <t>Carton Box</t>
+          <t>Aluminum, Brass, Non-Ferrous Alloys</t>
         </is>
       </c>
       <c r="FD3" t="inlineStr"/>
       <c r="FE3" t="inlineStr">
         <is>
-          <t>Unit Packaging Weight</t>
+          <t>Target Surface Finish</t>
         </is>
       </c>
       <c r="FF3" t="inlineStr">
         <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="FG3" t="inlineStr">
-        <is>
-          <t>lb</t>
-        </is>
-      </c>
+          <t>Clean Burr-Free Cut Edge</t>
+        </is>
+      </c>
+      <c r="FG3" t="inlineStr"/>
       <c r="FH3" t="inlineStr">
         <is>
-          <t>Country Of Origin</t>
+          <t>Primary Function</t>
         </is>
       </c>
       <c r="FI3" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>High-Speed Metal Cutting &amp; Severing</t>
         </is>
       </c>
       <c r="FJ3" t="inlineStr"/>
       <c r="FK3" t="inlineStr">
         <is>
-          <t>Discontinued</t>
+          <t>Package Quantity</t>
         </is>
       </c>
       <c r="FL3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>41</t>
         </is>
       </c>
       <c r="FM3" t="inlineStr"/>
       <c r="FN3" t="inlineStr">
         <is>
-          <t>Standard/Approvals</t>
+          <t>Package Type</t>
         </is>
       </c>
       <c r="FO3" t="inlineStr">
         <is>
-          <t>ANSI B7.1 Certified, OSHA Compliant, ISO 9001, RoHS</t>
+          <t>Carton Box</t>
         </is>
       </c>
       <c r="FP3" t="inlineStr"/>
       <c r="FQ3" t="inlineStr">
         <is>
-          <t>Safety Standard</t>
+          <t>Unit Packaging Weight</t>
         </is>
       </c>
       <c r="FR3" t="inlineStr">
         <is>
-          <t>ANSI B7.1 Safety Standard for Abrasive Wheels</t>
-        </is>
-      </c>
-      <c r="FS3" t="inlineStr"/>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="FS3" t="inlineStr">
+        <is>
+          <t>lb</t>
+        </is>
+      </c>
       <c r="FT3" t="inlineStr">
         <is>
-          <t>Quality Certification</t>
+          <t>Country Of Origin</t>
         </is>
       </c>
       <c r="FU3" t="inlineStr">
         <is>
-          <t>ISO 9001:2015 Quality Management System</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="FV3" t="inlineStr"/>
       <c r="FW3" t="inlineStr">
         <is>
-          <t>Environmental Compliance</t>
+          <t>Discontinued</t>
         </is>
       </c>
       <c r="FX3" t="inlineStr">
         <is>
-          <t>RoHS Directive 2011/65/EU Compliant</t>
+          <t>No</t>
         </is>
       </c>
       <c r="FY3" t="inlineStr"/>
       <c r="FZ3" t="inlineStr">
         <is>
-          <t>Prop 65</t>
+          <t>Safety Standard</t>
         </is>
       </c>
       <c r="GA3" t="inlineStr">
         <is>
-          <t>WARNING: Cancer and Reproductive Harm - www.P65Warnings.ca.gov</t>
+          <t>ANSI B7.1 Safety Standard for Abrasive Wheels</t>
         </is>
       </c>
       <c r="GB3" t="inlineStr"/>
       <c r="GC3" t="inlineStr">
         <is>
-          <t>Manufacturer Part Number</t>
+          <t>Quality Certification</t>
         </is>
       </c>
       <c r="GD3" t="inlineStr">
         <is>
-          <t>DBD090094101F</t>
+          <t>ISO 9001:2015 Quality Management System</t>
         </is>
       </c>
       <c r="GE3" t="inlineStr"/>
       <c r="GF3" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Environmental Compliance</t>
         </is>
       </c>
       <c r="GG3" t="inlineStr">
         <is>
-          <t>Black / Red</t>
+          <t>RoHS Directive 2011/65/EU Compliant</t>
         </is>
       </c>
       <c r="GH3" t="inlineStr"/>
       <c r="GI3" t="inlineStr">
         <is>
-          <t>Diameter</t>
+          <t>Prop 65</t>
         </is>
       </c>
       <c r="GJ3" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="GK3" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
+          <t>WARNING: Cancer and Reproductive Harm - www.P65Warnings.ca.gov</t>
+        </is>
+      </c>
+      <c r="GK3" t="inlineStr"/>
       <c r="GL3" t="inlineStr">
         <is>
-          <t>Arbor Size</t>
+          <t>Manufacturer Part Number</t>
         </is>
       </c>
       <c r="GM3" t="inlineStr">
         <is>
-          <t>7/8</t>
-        </is>
-      </c>
-      <c r="GN3" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
+          <t>DBD090094101F</t>
+        </is>
+      </c>
+      <c r="GN3" t="inlineStr"/>
       <c r="GO3" t="inlineStr">
         <is>
-          <t>Overall Dimensions</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="GP3" t="inlineStr">
         <is>
-          <t>9 in Dia x .045 in T</t>
+          <t>Black / Red</t>
         </is>
       </c>
       <c r="GQ3" t="inlineStr"/>
